--- a/tinHelm/excel/Dice.xlsx
+++ b/tinHelm/excel/Dice.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\COCOSproject\dice\tinHelm\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DHXM\Documents\dice\tinHelm\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="29790" windowHeight="10455"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/tinHelm/excel/Dice.xlsx
+++ b/tinHelm/excel/Dice.xlsx
@@ -1160,7 +1160,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="1">
-        <v>6001</v>
+        <v>1</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>15</v>
@@ -1179,7 +1179,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="1">
-        <v>6002</v>
+        <v>2</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>17</v>
@@ -1198,7 +1198,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="1">
-        <v>6003</v>
+        <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>19</v>
@@ -1217,7 +1217,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="1">
-        <v>6004</v>
+        <v>4</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>21</v>
@@ -1234,7 +1234,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="1">
-        <v>6005</v>
+        <v>5</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>23</v>
@@ -1251,7 +1251,7 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="1">
-        <v>6006</v>
+        <v>6</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>24</v>
@@ -1268,7 +1268,7 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="1">
-        <v>6007</v>
+        <v>7</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>25</v>
@@ -1285,7 +1285,7 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="1">
-        <v>6008</v>
+        <v>8</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>26</v>
@@ -1302,7 +1302,7 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="1">
-        <v>6009</v>
+        <v>9</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>27</v>
@@ -1319,7 +1319,7 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="1">
-        <v>6010</v>
+        <v>10</v>
       </c>
       <c r="B15" t="s">
         <v>28</v>
@@ -1336,7 +1336,7 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="1">
-        <v>6011</v>
+        <v>11</v>
       </c>
       <c r="B16" t="s">
         <v>29</v>
@@ -1353,7 +1353,7 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="1">
-        <v>6012</v>
+        <v>12</v>
       </c>
       <c r="B17" t="s">
         <v>30</v>
